--- a/doc/bug-report.xlsx
+++ b/doc/bug-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="207">
   <si>
     <t>#</t>
   </si>
@@ -528,6 +528,9 @@
     <t>Observe 3 merged bee enemies in bee room.</t>
   </si>
   <si>
+    <t>Set a max bullet size instead so that this situation does not happen.</t>
+  </si>
+  <si>
     <t>Most enemies are pretty centered, so manual offsets defined per enemt should be fine for now.</t>
   </si>
   <si>
@@ -621,7 +624,7 @@
     <t>33 - Push console replacing bullets</t>
   </si>
   <si>
-    <t>Occasionally, the push console replaces the latest bullet on the stack instead of giving a new one.</t>
+    <t>Occasionally, the push console replaces the latest bullet on the stack instead of giving a new one. NOTE: need to assess reproduceability to determine if bug is actually there.</t>
   </si>
   <si>
     <t>The push console should only add new bullets.</t>
@@ -13915,9 +13918,11 @@
         <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="G3" s="2" t="s">
         <v>86</v>
       </c>
@@ -13925,7 +13930,7 @@
         <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>89</v>
@@ -13957,7 +13962,7 @@
         <v>133</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>135</v>
@@ -13977,9 +13982,11 @@
         <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G5" s="2" t="s">
         <v>137</v>
       </c>
@@ -14045,13 +14052,13 @@
         <v>20</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>160</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>162</v>
@@ -14122,7 +14129,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>168</v>
@@ -14139,7 +14146,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" s="3">
         <v>45607.0</v>
@@ -14157,16 +14164,16 @@
         <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -14187,7 +14194,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" s="3">
         <v>45607.0</v>
@@ -14205,16 +14212,16 @@
         <v>20</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -14235,7 +14242,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B12" s="3">
         <v>45610.0</v>
@@ -14250,19 +14257,19 @@
         <v>12</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -14283,7 +14290,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B13" s="8">
         <v>45613.0</v>
@@ -14301,21 +14308,21 @@
         <v>32</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B14" s="3">
         <v>45613.0</v>
@@ -14331,16 +14338,16 @@
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -14361,7 +14368,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B15" s="3">
         <v>45613.0</v>
@@ -14377,16 +14384,16 @@
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -14405,12 +14412,18 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
+    <row r="16">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E16">
       <formula1>"Resolved,Open ,Won't Fix"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D16">
       <formula1>"P0,P1,P2,P3,P4,P5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/doc/bug-report.xlsx
+++ b/doc/bug-report.xlsx
@@ -6,6 +6,7 @@
     <sheet state="visible" name="M1" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="M2" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="M3" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="M4" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="234">
   <si>
     <t>#</t>
   </si>
@@ -634,6 +635,87 @@
   </si>
   <si>
     <t>Interact with the push console.</t>
+  </si>
+  <si>
+    <t>UPDATE: has been pinpointed to be related to particle system.</t>
+  </si>
+  <si>
+    <t>Pop console somehow pops a key out of nowhere. UPDATE: bug seems to not be reproduceable.</t>
+  </si>
+  <si>
+    <t>The push console overwrites the latest bullet at times. UPDATE: bug seems to not be reproduceable.</t>
+  </si>
+  <si>
+    <t>34 - if fail tutorial, can't progress</t>
+  </si>
+  <si>
+    <t>If the player fails in the tutorial, then the game does not restart properly and thinks the player cleared. However, they are then unable to proceed with the dialogue and get stuck.</t>
+  </si>
+  <si>
+    <t>Players should not get stuck if they cannot pass the tutorial.</t>
+  </si>
+  <si>
+    <t>Players can get stuck if they fail the tutorial.</t>
+  </si>
+  <si>
+    <t>Fail the tutorial fight.</t>
+  </si>
+  <si>
+    <t>35 - circle collider texture repeat</t>
+  </si>
+  <si>
+    <t>Circle collider texture repeats at certain times, especially when overlapping with other entities.</t>
+  </si>
+  <si>
+    <t>circle collider should not repeat</t>
+  </si>
+  <si>
+    <t>Circle collider repeats at times. FIXED: no longer treat collider textures as tile.</t>
+  </si>
+  <si>
+    <t>Turn collider visuals on with c and walk around</t>
+  </si>
+  <si>
+    <t>36 - occasional frame drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occasional frame drops a few min into game. Drops from 60 fps to 55. Occurs in all types of rooms. </t>
+  </si>
+  <si>
+    <t>Should have stable fps.</t>
+  </si>
+  <si>
+    <t>UPDATE: This specific case happens to Amanda's desktop due to screen tearing, unrelated to game. However, performance drop over all is noticeable on lower performance machines.</t>
+  </si>
+  <si>
+    <t>play game and walk around for a few minutes.</t>
+  </si>
+  <si>
+    <t>37 - game flicker on game start occasionally</t>
+  </si>
+  <si>
+    <t>On every 2nd time start new game from title when go to title from pause menu, black screen loading image does not show and can see game world for a split second.</t>
+  </si>
+  <si>
+    <t>Shouldn't see game world flicker. Consider proper loading screen.</t>
+  </si>
+  <si>
+    <t>Black loading screen isn't always there</t>
+  </si>
+  <si>
+    <t>38 - screen artifacts on edges when game paused</t>
+  </si>
+  <si>
+    <t>When game is paused, can see artifacts on screen edges</t>
+  </si>
+  <si>
+    <t>Consider lessening pause effects on edges.</t>
+  </si>
+  <si>
+    <t>Screen artifacts appear on edges when game paused, minor distraction.</t>
+  </si>
+  <si>
+    <t>Observe game (especially door symbols) when paused</t>
   </si>
 </sst>
 </file>
@@ -736,6 +818,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -14094,7 +14180,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>56</v>
@@ -14429,4 +14515,366 @@
   </dataValidations>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="8">
+        <v>45613.0</v>
+      </c>
+      <c r="C2" s="8">
+        <v>45616.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45613.0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45616.0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45613.0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>45616.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45615.0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>45627.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45620.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>45627.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="3">
+        <v>45620.0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>45627.0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45624.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>45627.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45624.0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>45627.0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E9">
+      <formula1>"Resolved,Open ,Won't Fix"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D9">
+      <formula1>"P0,P1,P2,P3,P4,P5"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>